--- a/artfynd/A 43119-2025 artfynd.xlsx
+++ b/artfynd/A 43119-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83641966</v>
+        <v>84949279</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>102987</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,17 +710,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Askö, P39, Vstm</t>
+          <t>Asköviken - Paradiset, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583284.7646600864</v>
+        <v>583328</v>
       </c>
       <c r="R2" t="n">
-        <v>6600628.01903366</v>
+        <v>6600617</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +742,24 @@
           <t>Västerås-Barkarö</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>BDFCFD8C-6077-4600-9BAA-D41D5F87A753</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-03-10</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-03-10</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,31 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Vincent Olofsson</t>
+          <t>Christer Sundström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Vincent Olofsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Christer Sundström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83660737</v>
+        <v>83574141</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,17 +821,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Askö, Vstm</t>
+          <t>Askö, P39, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583312.7598764759</v>
+        <v>583285</v>
       </c>
       <c r="R3" t="n">
-        <v>6600626.102722809</v>
+        <v>6600628</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,27 +855,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3EEE7E35-706E-4D7F-8CDA-4452CB01EF2D</t>
+          <t>BDFCFD8C-6077-4600-9BAA-D41D5F87A753</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lav och mossa</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +885,125 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ali Abuljadayel</t>
+          <t>Carina Edelo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ali Abuljadayel</t>
+          <t>Carina Edelo</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83641967</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Askö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>583313</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6600626</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västerås-Barkarö</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3EEE7E35-706E-4D7F-8CDA-4452CB01EF2D</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-03-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-03-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Vincent Olofsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vincent Olofsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
